--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:15:17+00:00</t>
+    <t>2026-06-15T08:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:40:43+00:00</t>
+    <t>2026-06-15T08:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:59:58+00:00</t>
+    <t>2026-06-18T07:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T07:59:27+00:00</t>
+    <t>2026-06-18T08:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:58+00:00</t>
+    <t>2026-06-18T08:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:27+00:00</t>
+    <t>2026-06-18T08:56:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:56:30+00:00</t>
+    <t>2026-06-18T10:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:39:29+00:00</t>
+    <t>2026-06-18T11:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:30:08+00:00</t>
+    <t>2026-06-23T16:45:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:45:59+00:00</t>
+    <t>2026-06-24T07:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:38:46+00:00</t>
+    <t>2026-06-25T15:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:26:12+00:00</t>
+    <t>2026-07-20T12:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet der zugelassenen Codes für die Intention einer onkologischen Therapielinie oder eines Behandlungsabschnitts.</t>
+    <t>Intention (das „Warum") einer onkologischen Therapielinie bzw. eines Behandlungsabschnitts.
+Verwendet aktuelle SNOMED-CT-Codes aus der Hierarchie `362961001 | Procedure by intent`.
+Die deutschen Anzeigetexte sind als Concept-Display hinterlegt (Übersetzung der englischen
+SNOMED-FSN). Extensible gebunden – seltene Sonderintentionen dürfen ergänzt werden.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,10 +102,37 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>373808002</t>
+  </si>
+  <si>
+    <t>Kurativ</t>
+  </si>
+  <si>
+    <t>363676003</t>
+  </si>
+  <si>
+    <t>Palliativ</t>
+  </si>
+  <si>
+    <t>373847000</t>
+  </si>
+  <si>
+    <t>Neoadjuvant</t>
+  </si>
+  <si>
+    <t>373846009</t>
+  </si>
+  <si>
+    <t>Adjuvant</t>
+  </si>
+  <si>
+    <t>399707004</t>
+  </si>
+  <si>
+    <t>Supportiv</t>
   </si>
   <si>
     <t/>
@@ -111,7 +141,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://bih-cei.de/fhir/therapieziele-onkologie/CodeSystem/onko-therapy-intent</t>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -375,7 +405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -386,26 +416,64 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,8 +86,9 @@
   <si>
     <t>Intention (das „Warum") einer onkologischen Therapielinie bzw. eines Behandlungsabschnitts.
 Verwendet aktuelle SNOMED-CT-Codes aus der Hierarchie `362961001 | Procedure by intent`.
-Die deutschen Anzeigetexte sind als Concept-Display hinterlegt (Übersetzung der englischen
-SNOMED-FSN). Extensible gebunden – seltene Sonderintentionen dürfen ergänzt werden.</t>
+Als Concept-Display dient der englische SNOMED-Anzeigetext des aktuellen Release (validierbar
+gegen tx.fhir.org); die deutschen Begriffe stehen in den Label-Texten
+des Leitfadens. Extensible gebunden – seltene Sonderintentionen dürfen ergänzt werden.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,31 +109,31 @@
     <t>373808002</t>
   </si>
   <si>
-    <t>Kurativ</t>
+    <t>Curative - procedure intent</t>
   </si>
   <si>
     <t>363676003</t>
   </si>
   <si>
-    <t>Palliativ</t>
+    <t>Palliative intent</t>
   </si>
   <si>
     <t>373847000</t>
   </si>
   <si>
-    <t>Neoadjuvant</t>
+    <t>Neoadjuvant intent</t>
   </si>
   <si>
     <t>373846009</t>
   </si>
   <si>
-    <t>Adjuvant</t>
+    <t>Adjuvant - intent</t>
   </si>
   <si>
     <t>399707004</t>
   </si>
   <si>
-    <t>Supportiv</t>
+    <t>Supportive - procedure intent</t>
   </si>
   <si>
     <t/>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
